--- a/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
+++ b/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
+++ b/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8 - 5</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
+++ b/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="33.0"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="55.00000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -265,21 +265,21 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 18, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>08:30 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Manhattan SC Inter B2014/15</t>
+          <t>River Island FC 2015/2016 RAVENS</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Nyland</t>
+          <t>Manhattan SC Inter B2014/15</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Roosevelt Island- Octagon Field - Octagon Field</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -310,21 +310,21 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Saturday, October 31, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>08:30 EDT</t>
+          <t>16:00 EDT</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>River Island FC 2015/2016 RAVENS</t>
+          <t>UNITED CYCLONES FC Geo 2014/15</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -339,7 +339,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Roosevelt Island- Octagon Field - Octagon Field</t>
+          <t>Bill Brown Playground - 1</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -349,27 +349,27 @@
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Sunday, November  1, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>16:00 EDT</t>
+          <t>15:30 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>UNITED CYCLONES FC Geo 2014/15</t>
+          <t>Manhattan SC Inter B2014/15</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +379,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>Manhattan SC Inter B2014/15</t>
+          <t>SC Gjoa Nyland</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - 1</t>
+          <t>Randall's Island - 10A - Icahn</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -394,7 +394,7 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
+++ b/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
@@ -175,36 +175,36 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>13:30 EDT</t>
+          <t>15:00 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>Manhattan SC Inter B2014/15</t>
+          <t>FC Copa Academy Brooklyn B14/15 Black</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8 - 5</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>UNITED CYCLONES FC Geo 2014/15</t>
+          <t>Manhattan SC Inter B2014/15</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Randall's Island - 10 - Icahn</t>
+          <t>Aviator Sports &amp; Events Center - Aviator Sports &amp; Events Center Field #2A</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,32 +214,32 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>15:00 EDT</t>
+          <t>08:30 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>FC Copa Academy Brooklyn B14/15 Black</t>
+          <t>River Island FC 2015/2016 RAVENS</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>8 - 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -249,7 +249,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Aviator Sports &amp; Events Center - Aviator Sports &amp; Events Center Field #2A</t>
+          <t>Roosevelt Island- Octagon Field - Octagon Field</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -265,21 +265,21 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Sunday, November  1, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>08:30 EDT</t>
+          <t>15:30 EST</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>River Island FC 2015/2016 RAVENS</t>
+          <t>Manhattan SC Inter B2014/15</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>Manhattan SC Inter B2014/15</t>
+          <t>SC Gjoa Nyland</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Roosevelt Island- Octagon Field - Octagon Field</t>
+          <t>Randall's Island - 10A - Icahn</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -304,27 +304,27 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Sunday, November  8, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>16:00 EDT</t>
+          <t>16:30 EST</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>UNITED CYCLONES FC Geo 2014/15</t>
+          <t>Manhattan SC Inter B2014/15</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Manhattan SC Inter B2014/15</t>
+          <t>FC Copa Academy Brooklyn B14/15 Black</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - 1</t>
+          <t>Randall's Island - 10 - Icahn</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -349,27 +349,27 @@
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November  1, 2026</t>
+          <t>Saturday, November 14, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>15:30 EST</t>
+          <t>08:00 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>Manhattan SC Inter B2014/15</t>
+          <t>SC Gjoa Nyland</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +379,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Nyland</t>
+          <t>Manhattan SC Inter B2014/15</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>Randall's Island - 10A - Icahn</t>
+          <t>Dyker Turf Field B Small Sided  - B</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -394,22 +394,22 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>Rescheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November  8, 2026</t>
+          <t>Sunday, November 15, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>16:30 EST</t>
+          <t>14:00 EST</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>FC Copa Academy Brooklyn B14/15 Black</t>
+          <t>UNITED CYCLONES FC Geo 2014/15</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>Randall's Island - 10 - Icahn</t>
+          <t>Randall's Island - 8</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -439,27 +439,27 @@
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November 14, 2026</t>
+          <t>Sunday, November 22, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>08:00 EST</t>
+          <t>08:40 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Nyland</t>
+          <t>UNITED CYCLONES FC Geo 2014/15</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field B Small Sided  - B</t>
+          <t>Bill Brown Playground - 1</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
+++ b/data/2026/cjsl/fall/manhattan-sc-inter-b2014-15.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 - 2</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
